--- a/data/trans_orig/P37A$vacunapreferencia-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunapreferencia-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476524</t>
+          <t>476002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490043</t>
+          <t>489901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452812</t>
+          <t>452827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464635</t>
+          <t>464452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>934415</t>
+          <t>934684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>952581</t>
+          <t>952294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>712073</t>
+          <t>713431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728194</t>
+          <t>728233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609112</t>
+          <t>610694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622507</t>
+          <t>622594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1330289</t>
+          <t>1329411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1348378</t>
+          <t>1349043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615576</t>
+          <t>616720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631860</t>
+          <t>631258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659488</t>
+          <t>659163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678654</t>
+          <t>678457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1281880</t>
+          <t>1280475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1305833</t>
+          <t>1305356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493091</t>
+          <t>492043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510544</t>
+          <t>510522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498422</t>
+          <t>498337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510845</t>
+          <t>511466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996362</t>
+          <t>998661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1018027</t>
+          <t>1017950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30633</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27143</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51793</t>
+          <t>52310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358528</t>
+          <t>357786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375243</t>
+          <t>375215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373353</t>
+          <t>375058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392341</t>
+          <t>392180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>738903</t>
+          <t>738386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763553</t>
+          <t>763490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22056</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41224</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270527</t>
+          <t>268779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285433</t>
+          <t>284124</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>319836</t>
+          <t>319737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334610</t>
+          <t>334102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>594293</t>
+          <t>595964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615591</t>
+          <t>615448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>195396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206233</t>
+          <t>206492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>317713</t>
+          <t>317469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330461</t>
+          <t>330837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>517070</t>
+          <t>517832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>534597</t>
+          <t>535036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3163424</t>
+          <t>3165171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3201724</t>
+          <t>3203179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3271122</t>
+          <t>3273404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3311652</t>
+          <t>3309517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6449899</t>
+          <t>6448552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6504456</t>
+          <t>6503594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437828</t>
+          <t>437046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450173</t>
+          <t>449465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415562</t>
+          <t>416002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428231</t>
+          <t>428150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>859391</t>
+          <t>858948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>876380</t>
+          <t>875496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670817</t>
+          <t>670277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682891</t>
+          <t>682818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592453</t>
+          <t>593112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605352</t>
+          <t>605379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268903</t>
+          <t>1268762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1285504</t>
+          <t>1285397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648942</t>
+          <t>648062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668162</t>
+          <t>668410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691632</t>
+          <t>690795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704888</t>
+          <t>704787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1346286</t>
+          <t>1344949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1369228</t>
+          <t>1370099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>38971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588849</t>
+          <t>589527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605436</t>
+          <t>605327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595618</t>
+          <t>597070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611818</t>
+          <t>611011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1191552</t>
+          <t>1191845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214919</t>
+          <t>1214042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>17502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37519</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403000</t>
+          <t>403721</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419014</t>
+          <t>419250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431303</t>
+          <t>430988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443691</t>
+          <t>443671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839710</t>
+          <t>838961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859590</t>
+          <t>859727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>29257</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279308</t>
+          <t>280529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297236</t>
+          <t>296858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330181</t>
+          <t>330014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345180</t>
+          <t>345117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616208</t>
+          <t>616240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>639465</t>
+          <t>638880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227786</t>
+          <t>227420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243658</t>
+          <t>244459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376225</t>
+          <t>375376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386833</t>
+          <t>385865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608814</t>
+          <t>610116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629224</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126484</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147335</t>
+          <t>146471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>199000</t>
+          <t>200010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3300295</t>
+          <t>3301253</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3340663</t>
+          <t>3342967</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3469625</t>
+          <t>3473287</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3504681</t>
+          <t>3505351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6786088</t>
+          <t>6785078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6837753</t>
+          <t>6838617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,47 +6706,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8398</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7720</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410792</t>
+          <t>410742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418476</t>
+          <t>418553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,49 +6819,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>392869</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>387357</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>394818</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>99,76%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>392869</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>388035</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>394815</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>790</t>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802347</t>
+          <t>801836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812414</t>
+          <t>812327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577741</t>
+          <t>578357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588533</t>
+          <t>588595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>550716</t>
+          <t>549618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561589</t>
+          <t>561058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1133543</t>
+          <t>1133567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1147346</t>
+          <t>1147659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662699</t>
+          <t>661822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648866</t>
+          <t>648161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659413</t>
+          <t>659443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316596</t>
+          <t>1314271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327104</t>
+          <t>1327493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626810</t>
+          <t>626119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642112</t>
+          <t>641230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636487</t>
+          <t>635844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646918</t>
+          <t>646944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1268815</t>
+          <t>1268856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286180</t>
+          <t>1285926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457525</t>
+          <t>458747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472556</t>
+          <t>472621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472161</t>
+          <t>471200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489557</t>
+          <t>489040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935612</t>
+          <t>936352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>958415</t>
+          <t>958673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,47 +8456,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>26588</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>17250</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>37828</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>26588</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>17922</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>39306</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315702</t>
+          <t>314822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328499</t>
+          <t>328282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353226</t>
+          <t>354130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368635</t>
+          <t>369603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,47 +8569,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>685504</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>674264</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>694842</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>97,58%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>685504</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>672786</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>694170</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239313</t>
+          <t>239050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250804</t>
+          <t>250779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>378146</t>
+          <t>377647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>393800</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620866</t>
+          <t>622188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>641660</t>
+          <t>641293</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82588</t>
+          <t>82379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98108</t>
+          <t>98580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>142538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3321307</t>
+          <t>3323557</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3351755</t>
+          <t>3353076</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3461954</t>
+          <t>3462163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3495417</t>
+          <t>3495801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6795669</t>
+          <t>6796354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6840784</t>
+          <t>6840312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25894</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27610</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398626</t>
+          <t>406043</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392868</t>
+          <t>398277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>300188</t>
+          <t>348964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287306</t>
+          <t>336995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308118</t>
+          <t>355982</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>698814</t>
+          <t>755008</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685577</t>
+          <t>741425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706050</t>
+          <t>762791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>33804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44070</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50875</t>
+          <t>59128</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>42633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70948</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>402379</t>
+          <t>451567</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386203</t>
+          <t>435678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411870</t>
+          <t>461666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>482386</t>
+          <t>467929</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468023</t>
+          <t>452987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495762</t>
+          <t>479219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>884765</t>
+          <t>919495</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>864692</t>
+          <t>899628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>900430</t>
+          <t>935990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40080</t>
+          <t>44704</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>60874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68305</t>
+          <t>76220</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>94219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>496258</t>
+          <t>576133</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482883</t>
+          <t>559963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508802</t>
+          <t>589431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>563777</t>
+          <t>591677</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553224</t>
+          <t>579902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>572855</t>
+          <t>599874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1060035</t>
+          <t>1167809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1042356</t>
+          <t>1149810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075851</t>
+          <t>1184454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>52226</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>38877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73086</t>
+          <t>68551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>64334</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>53519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106027</t>
+          <t>116560</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>99416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135461</t>
+          <t>136249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>840526</t>
+          <t>648391</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814700</t>
+          <t>632066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868300</t>
+          <t>661740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>654114</t>
+          <t>672552</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640689</t>
+          <t>660011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666449</t>
+          <t>683367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1494640</t>
+          <t>1320944</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1465206</t>
+          <t>1301255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1538476</t>
+          <t>1338088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72728</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>61206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88190</t>
+          <t>92835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67560</t>
+          <t>76235</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>63515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81185</t>
+          <t>88565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>140288</t>
+          <t>153280</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122508</t>
+          <t>135779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160264</t>
+          <t>176999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>488506</t>
+          <t>532301</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>473044</t>
+          <t>516511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501763</t>
+          <t>548140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>480345</t>
+          <t>532620</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466720</t>
+          <t>520290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490226</t>
+          <t>545340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>968851</t>
+          <t>1064922</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948875</t>
+          <t>1041203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>986631</t>
+          <t>1082423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47897</t>
+          <t>52594</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38217</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59258</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>49453</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73149</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>92526</t>
+          <t>102048</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>86956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122146</t>
+          <t>119644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>320268</t>
+          <t>354486</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308907</t>
+          <t>342075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329948</t>
+          <t>365411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>563738</t>
+          <t>389713</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>535219</t>
+          <t>379557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588954</t>
+          <t>398973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>884007</t>
+          <t>744198</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>854387</t>
+          <t>726602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>926578</t>
+          <t>759290</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30885</t>
+          <t>32255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>60304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>261400</t>
+          <t>286561</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252751</t>
+          <t>278009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267929</t>
+          <t>293730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>402639</t>
+          <t>439953</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>432354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>409004</t>
+          <t>446121</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>664039</t>
+          <t>726515</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>652703</t>
+          <t>714503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>672561</t>
+          <t>736963</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199770</t>
+          <t>245821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288312</t>
+          <t>310395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>211722</t>
+          <t>266758</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>296987</t>
+          <t>325441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>448678</t>
+          <t>530256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>571131</t>
+          <t>616274</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3207965</t>
+          <t>3255484</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3171505</t>
+          <t>3222367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3260047</t>
+          <t>3286941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,34 +12214,34 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3447186</t>
+          <t>3443408</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3415293</t>
+          <t>3411513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3500558</t>
+          <t>3470196</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>92,86%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>8018</t>
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6655151</t>
+          <t>6698892</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6600966</t>
+          <t>6653442</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6723419</t>
+          <t>6739460</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
